--- a/docs/نموذج-العامل.xlsx
+++ b/docs/نموذج-العامل.xlsx
@@ -10,7 +10,7 @@
   <sheets>
     <sheet name="نموذج العامل" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="مطابقة الوردية مع الطلب" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="البيانات" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="بيانات الورديات" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -111,7 +111,7 @@
     <t xml:space="preserve">نعم</t>
   </si>
   <si>
-    <t xml:space="preserve">يحمي نسبة الـ١٥٪ — انظر أسفل الملخص</t>
+    <t xml:space="preserve">يحمي نسبة الـ١٥٪</t>
   </si>
   <si>
     <t xml:space="preserve">② بطاقة العامل — اختر الوردية فيُشتق خط الأساس · عبّئ الفعلي وبوابة الجودة</t>
@@ -378,7 +378,7 @@
     <t xml:space="preserve">•  غياب قياس زمن الخدمة يفرّغ بوابة الجودة من معناها</t>
   </si>
   <si>
-    <t xml:space="preserve">•  احتساب الحافز على الحجم الكلي يكافئ الموسم لا الأداء</t>
+    <t xml:space="preserve">•  الصرف في شهر صافيه سالب — الحافز فردي والشركة تقبض الصافي</t>
   </si>
   <si>
     <t xml:space="preserve">مطابقة الوردية مع الطلب</t>
@@ -444,7 +444,7 @@
     <t xml:space="preserve">•  السبب أن العمالة موزّعة ٥٠/٥٠ بينما الطلب المسائي ٥٥–٥٦٪ من الزيارات</t>
   </si>
   <si>
-    <t xml:space="preserve">•  المعيصم وحدها متوازنة (٥٠.٤٪ مساءً) — لأن ذروتها ٥ إلى ٧ مساءً لا بعد التاسعة</t>
+    <t xml:space="preserve">•  المعيصم وحدها متوازنة — لأن ذروتها ٥ إلى ٧ مساءً لا بعد التاسعة</t>
   </si>
   <si>
     <t xml:space="preserve">لماذا يهم هذا في نموذج الحافز</t>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="6" t="str">
-        <f aca="false">IFERROR("ذروة "&amp;INDEX(البيانات!$I$4:$I$8,MATCH($C$4,البيانات!$B$4:$B$8,0)),"")</f>
+        <f aca="false">IFERROR("ذروة "&amp;INDEX('بيانات الورديات'!$I$4:$I$8,MATCH($C$4,'بيانات الورديات'!$B$4:$B$8,0)),"")</f>
         <v/>
       </c>
       <c r="E4" s="7" t="s">
@@ -1399,7 +1399,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="8" t="n">
-        <f aca="false">IFERROR(INDEX(البيانات!$C$4:$C$8,MATCH($C$4,البيانات!$B$4:$B$8,0)),0)</f>
+        <f aca="false">IFERROR(INDEX('بيانات الورديات'!$C$4:$C$8,MATCH($C$4,'بيانات الورديات'!$B$4:$B$8,0)),0)</f>
         <v>0</v>
       </c>
       <c r="E6" s="7" t="s">
@@ -1411,7 +1411,7 @@
         <v>9</v>
       </c>
       <c r="C7" s="9" t="n">
-        <f aca="false">IFERROR(INDEX(البيانات!$D$4:$D$8,MATCH($C$4,البيانات!$B$4:$B$8,0)),0)</f>
+        <f aca="false">IFERROR(INDEX('بيانات الورديات'!$D$4:$D$8,MATCH($C$4,'بيانات الورديات'!$B$4:$B$8,0)),0)</f>
         <v>0</v>
       </c>
       <c r="E7" s="7" t="s">
@@ -1423,7 +1423,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="10" t="n">
-        <f aca="false">IFERROR(INDEX(البيانات!$E$4:$E$8,MATCH($C$4,البيانات!$B$4:$B$8,0)),0)</f>
+        <f aca="false">IFERROR(INDEX('بيانات الورديات'!$E$4:$E$8,MATCH($C$4,'بيانات الورديات'!$B$4:$B$8,0)),0)</f>
         <v>0</v>
       </c>
       <c r="E8" s="7" t="s">
@@ -1435,7 +1435,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="10" t="n">
-        <f aca="false">IFERROR(INDEX(البيانات!$F$4:$F$8,MATCH($C$4,البيانات!$B$4:$B$8,0)),0)</f>
+        <f aca="false">IFERROR(INDEX('بيانات الورديات'!$F$4:$F$8,MATCH($C$4,'بيانات الورديات'!$B$4:$B$8,0)),0)</f>
         <v>0</v>
       </c>
       <c r="E9" s="7" t="s">
@@ -1447,7 +1447,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="11" t="n">
-        <f aca="false">IFERROR(INDEX(البيانات!$G$4:$G$8,MATCH($C$4,البيانات!$B$4:$B$8,0)),0)</f>
+        <f aca="false">IFERROR(INDEX('بيانات الورديات'!$G$4:$G$8,MATCH($C$4,'بيانات الورديات'!$B$4:$B$8,0)),0)</f>
         <v>0</v>
       </c>
       <c r="E10" s="7" t="s">
@@ -1459,7 +1459,7 @@
         <v>17</v>
       </c>
       <c r="C11" s="11" t="n">
-        <f aca="false">IFERROR(INDEX(البيانات!$H$4:$H$8,MATCH($C$4,البيانات!$B$4:$B$8,0)),0)</f>
+        <f aca="false">IFERROR(INDEX('بيانات الورديات'!$H$4:$H$8,MATCH($C$4,'بيانات الورديات'!$B$4:$B$8,0)),0)</f>
         <v>0</v>
       </c>
       <c r="E11" s="7" t="s">
@@ -3036,7 +3036,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4BAE163F-AE60-41A5-AC2E-6E5B2A455EAB}</x14:id>
+          <x14:id>{E8DE3F7D-D783-44FF-80DB-CF78C8DBF710}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3102,7 +3102,7 @@
   </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation allowBlank="true" error="اختر محطة من القائمة" errorStyle="stop" errorTitle="قيمة غير معتمدة" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C4" type="list">
-      <formula1>البيانات!$B$4:$B$8</formula1>
+      <formula1>'بيانات الورديات'!$B$4:$B$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C17" type="list">
@@ -3110,11 +3110,11 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C21:C40" type="list">
-      <formula1>البيانات!$Q$4:$Q$5</formula1>
+      <formula1>'بيانات الورديات'!$Q$4:$Q$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="اكتب: مستوفاة أو غير مستوفاة" errorStyle="stop" errorTitle="قيمة غير معتمدة" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J21:J40" type="list">
-      <formula1>البيانات!$R$4:$R$5</formula1>
+      <formula1>'بيانات الورديات'!$R$4:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -3129,7 +3129,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4BAE163F-AE60-41A5-AC2E-6E5B2A455EAB}">
+          <x14:cfRule type="dataBar" id="{E8DE3F7D-D783-44FF-80DB-CF78C8DBF710}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/docs/نموذج-العامل.xlsx
+++ b/docs/نموذج-العامل.xlsx
@@ -585,7 +585,7 @@
     <numFmt numFmtId="174" formatCode="0%"/>
     <numFmt numFmtId="175" formatCode="\+0.0%;\-0.0%"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -611,51 +611,52 @@
     <font>
       <b val="true"/>
       <sz val="16"/>
-      <color rgb="FF1F3864"/>
-      <name val="Arial"/>
+      <color rgb="FF55565A"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF44546A"/>
-      <name val="Arial"/>
+      <color rgb="FF6E6A64"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="12"/>
-      <color rgb="FF1F3864"/>
-      <name val="Arial"/>
+      <color rgb="FFF5831F"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <name val="Arial"/>
+      <color rgb="FF3D3D3D"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
+      <color rgb="FF3E6E8E"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF44546A"/>
-      <name val="Arial"/>
+      <color rgb="FF9B968E"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
-      <name val="Arial"/>
+      <color rgb="FF2E8B6F"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -663,28 +664,35 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <color rgb="FF3D3D3D"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FFC00000"/>
-      <name val="Arial"/>
+      <color rgb="FF9A3E2C"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF1F3864"/>
-      <name val="Arial"/>
+      <color rgb="FF55565A"/>
+      <name val="DIN Next Arabic"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -692,7 +700,7 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FFC00000"/>
-      <name val="Arial"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -706,32 +714,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-        <bgColor rgb="FFD9E2F3"/>
+        <fgColor rgb="FFFBEEE0"/>
+        <bgColor rgb="FFF5F2ED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFCE7C8"/>
+        <bgColor rgb="FFFBEEE0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFF5F2ED"/>
+        <bgColor rgb="FFFBEEE0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
-        <bgColor rgb="FF333399"/>
+        <fgColor rgb="FF55565A"/>
+        <bgColor rgb="FF6E6A64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E2F3"/>
-        <bgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFEDE7DE"/>
+        <bgColor rgb="FFFBEEE0"/>
       </patternFill>
     </fill>
   </fills>
@@ -745,29 +753,29 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFE3DCD1"/>
       </left>
       <right/>
       <top style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFE3DCD1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFE3DCD1"/>
       </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFE3DCD1"/>
       </left>
       <right style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFE3DCD1"/>
       </right>
       <top style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFE3DCD1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFE3DCD1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -938,11 +946,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -978,88 +986,88 @@
   <dxfs count="7">
     <dxf>
       <font>
-        <name val="Arial"/>
+        <name val="DIN Next Arabic"/>
         <charset val="1"/>
         <family val="0"/>
-        <color rgb="FF375623"/>
+        <color rgb="FF1F5E4A"/>
         <sz val="10"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
+          <bgColor rgb="FFD6E9E1"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <name val="Arial"/>
+        <name val="DIN Next Arabic"/>
         <charset val="1"/>
         <family val="0"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF9A3E2C"/>
         <sz val="10"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FFF2DAD4"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <name val="Arial"/>
+        <name val="DIN Next Arabic"/>
         <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
-        <color rgb="FF375623"/>
+        <color rgb="FF1F5E4A"/>
         <sz val="10"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
+          <bgColor rgb="FFD6E9E1"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <name val="Arial"/>
+        <name val="DIN Next Arabic"/>
         <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
-        <color rgb="FF833C00"/>
+        <color rgb="FFA8681A"/>
         <sz val="10"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFE699"/>
+          <bgColor rgb="FFFCE7C8"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
+          <bgColor rgb="FFD6E9E1"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <name val="Arial"/>
+        <name val="DIN Next Arabic"/>
         <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF9A3E2C"/>
         <sz val="10"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FFF2DAD4"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFE699"/>
+          <bgColor rgb="FFFCE7C8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1077,51 +1085,51 @@
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FFA8681A"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFBFBFBF"/>
+      <rgbColor rgb="FF1F5E4A"/>
+      <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FFDDEBF7"/>
+      <rgbColor rgb="FFFBEEE0"/>
+      <rgbColor rgb="FFF5F2ED"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9E2F3"/>
+      <rgbColor rgb="FFE3DCD1"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF3E6E8E"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFC6E0B4"/>
-      <rgbColor rgb="FFFFE699"/>
+      <rgbColor rgb="FFEDE7DE"/>
+      <rgbColor rgb="FFD6E9E1"/>
+      <rgbColor rgb="FFFCE7C8"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFF8CBAD"/>
+      <rgbColor rgb="FFF2DAD4"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFF5831F"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF44546A"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF1F3864"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF6E6A64"/>
+      <rgbColor rgb="FF9B968E"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF2E8B6F"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF833C00"/>
+      <rgbColor rgb="FF9A3E2C"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF375623"/>
+      <rgbColor rgb="FF55565A"/>
+      <rgbColor rgb="FF3D3D3D"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1305,7 +1313,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:L88"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -1340,7 +1348,7 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -3032,11 +3040,11 @@
       <dataBar showValue="1" minLength="10" maxLength="90">
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1.3"/>
-        <color rgb="FF5B9BD5"/>
+        <color rgb="FFF5831F"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{E8DE3F7D-D783-44FF-80DB-CF78C8DBF710}</x14:id>
+          <x14:id>{61FF7BE3-12A7-4C3B-A24A-56E9929C67CF}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3118,9 +3126,9 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3129,7 +3137,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{E8DE3F7D-D783-44FF-80DB-CF78C8DBF710}">
+          <x14:cfRule type="dataBar" id="{61FF7BE3-12A7-4C3B-A24A-56E9929C67CF}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -3137,7 +3145,7 @@
               <x14:cfvo type="num">
                 <xm:f>1.3</xm:f>
               </x14:cfvo>
-              <x14:negativeFillColor rgb="FF5B9BD5"/>
+              <x14:negativeFillColor rgb="FFF5831F"/>
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
@@ -3152,7 +3160,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:L23"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -3182,7 +3190,7 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>120</v>
       </c>
@@ -3592,13 +3600,13 @@
         <cfvo type="min" val="0"/>
         <cfvo type="max" val="0"/>
         <color rgb="FFFFFFFF"/>
-        <color rgb="FFF8CBAD"/>
+        <color rgb="FFF2DAD4"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3609,7 +3617,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:R11"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -3648,7 +3656,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>150</v>
       </c>
@@ -3982,9 +3990,9 @@
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
